--- a/11_Tables/Table1 Function.xlsx
+++ b/11_Tables/Table1 Function.xlsx
@@ -24,21 +24,21 @@
   <numFmts count="0"/>
   <fonts count="29">
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="134"/>
       <color theme="1"/>
       <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="1"/>
@@ -67,20 +67,20 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="华文琥珀"/>
+      <name val="STHupo"/>
       <charset val="134"/>
       <color theme="9"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
@@ -88,7 +88,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
@@ -96,14 +96,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -111,7 +111,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
@@ -119,7 +119,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -127,7 +127,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -135,7 +135,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -143,14 +143,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
@@ -158,7 +158,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
@@ -166,7 +166,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
@@ -174,14 +174,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <b val="1"/>
       <color theme="1"/>
@@ -189,35 +189,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <color theme="0"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -885,55 +885,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent 1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent 2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent 3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent 4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent 5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1055,8 +1055,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1090,8 +1090,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t>/data1/liyaru/投稿/Manuscript_0107_NM/Tables/Table1 Function.xlsx</t>
+          <t>Historical file URI (UTF-8 encoded): file:///data1/liyaru/%E6%8A%95%E7%A8%BF/Manuscript_0107_NM/Tables/Table1%20Function.xlsx</t>
         </is>
       </c>
     </row>
